--- a/data/trans_bre/IMC_inf_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_R2-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 11,09</t>
+          <t>-13,19; 11,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,99; 9,56</t>
+          <t>-17,61; 10,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,06; 0,87</t>
+          <t>-27,75; 1,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 5,4</t>
+          <t>-15,67; 5,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-28,44; 38,67</t>
+          <t>-31,67; 36,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,56; 23,92</t>
+          <t>-32,25; 28,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-53,97; 1,93</t>
+          <t>-53,58; 3,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-46,76; 26,12</t>
+          <t>-45,76; 24,34</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 6,56</t>
+          <t>-17,5; 8,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,79; -9,55</t>
+          <t>-36,01; -8,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-26,39; -3,29</t>
+          <t>-25,84; -4,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,44; 0,5</t>
+          <t>-23,39; 1,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,32; 20,6</t>
+          <t>-40,02; 26,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,98; -19,66</t>
+          <t>-57,83; -17,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,11; -9,28</t>
+          <t>-60,1; -9,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,8; 1,49</t>
+          <t>-50,64; 3,17</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-30,46; -4,48</t>
+          <t>-32,03; -4,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-27,74; 1,79</t>
+          <t>-29,08; -0,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-30,36; -0,98</t>
+          <t>-29,44; -1,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 7,59</t>
+          <t>-26,15; 8,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,22; -10,04</t>
+          <t>-57,42; -10,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,44; 4,84</t>
+          <t>-51,94; -1,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-58,75; -1,72</t>
+          <t>-57,21; -2,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-50,82; 20,58</t>
+          <t>-51,41; 24,24</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,47; -2,08</t>
+          <t>-18,54; -1,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,85; -1,51</t>
+          <t>-19,51; -1,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 9,84</t>
+          <t>-9,31; 8,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,22; -3,44</t>
+          <t>-28,97; -2,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,47; -4,55</t>
+          <t>-35,6; -3,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,42; -2,61</t>
+          <t>-33,48; -3,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 27,13</t>
+          <t>-20,34; 23,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,96; -8,81</t>
+          <t>-57,66; -8,31</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 11,14</t>
+          <t>-10,39; 12,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 17,38</t>
+          <t>-4,94; 18,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,51; -0,45</t>
+          <t>-21,1; -0,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 7,67</t>
+          <t>-18,1; 7,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-22,46; 29,39</t>
+          <t>-21,87; 33,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 48,31</t>
+          <t>-10,49; 52,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-39,93; -0,99</t>
+          <t>-39,23; -0,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-39,85; 24,99</t>
+          <t>-39,59; 22,35</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-41,95; -13,64</t>
+          <t>-40,91; -15,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 9,98</t>
+          <t>-24,01; 11,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-30,32; 0,5</t>
+          <t>-30,02; 1,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-32,46; -5,84</t>
+          <t>-32,12; -5,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,72; -29,38</t>
+          <t>-67,24; -31,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,25; 24,91</t>
+          <t>-41,78; 25,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-54,84; 1,34</t>
+          <t>-55,28; 2,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-75,2; -17,05</t>
+          <t>-74,98; -17,8</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,67; -5,06</t>
+          <t>-13,91; -4,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,51; -3,7</t>
+          <t>-13,34; -3,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,22; -4,56</t>
+          <t>-13,82; -3,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,78; -4,51</t>
+          <t>-16,26; -4,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-31,12; -11,71</t>
+          <t>-29,27; -11,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,27; -7,57</t>
+          <t>-25,09; -6,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-30,96; -11,07</t>
+          <t>-30,62; -9,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-38,56; -12,97</t>
+          <t>-39,15; -13,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_R2-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado</t>
+          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 11,24</t>
+          <t>-12,23; 10,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 10,82</t>
+          <t>-19,29; 8,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,75; 1,33</t>
+          <t>-27,24; 0,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 5,06</t>
+          <t>-15,5; 5,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-31,67; 36,2</t>
+          <t>-30,08; 33,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,25; 28,38</t>
+          <t>-35,0; 20,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-53,58; 3,75</t>
+          <t>-53,64; 0,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-45,76; 24,34</t>
+          <t>-48,26; 23,94</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 8,02</t>
+          <t>-17,9; 7,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,01; -8,57</t>
+          <t>-34,91; -8,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,84; -4,11</t>
+          <t>-25,71; -2,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,39; 1,33</t>
+          <t>-24,97; 0,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,02; 26,5</t>
+          <t>-40,43; 25,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,83; -17,41</t>
+          <t>-56,89; -17,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,1; -9,3</t>
+          <t>-57,73; -5,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,64; 3,17</t>
+          <t>-50,76; 2,37</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-32,03; -4,72</t>
+          <t>-30,41; -4,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-29,08; -0,68</t>
+          <t>-27,69; 0,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-29,44; -1,21</t>
+          <t>-30,0; -1,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-26,15; 8,53</t>
+          <t>-27,5; 7,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-57,42; -10,05</t>
+          <t>-56,45; -10,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-51,94; -1,65</t>
+          <t>-49,98; 2,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-57,21; -2,84</t>
+          <t>-57,11; -4,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-51,41; 24,24</t>
+          <t>-52,69; 23,1</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,54; -1,85</t>
+          <t>-19,16; -1,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,51; -1,76</t>
+          <t>-20,18; -2,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 8,69</t>
+          <t>-8,25; 9,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,97; -2,91</t>
+          <t>-27,29; -1,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,6; -3,78</t>
+          <t>-36,67; -4,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,48; -3,2</t>
+          <t>-34,56; -4,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 23,83</t>
+          <t>-18,48; 25,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-57,66; -8,31</t>
+          <t>-55,74; -5,3</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 12,25</t>
+          <t>-11,17; 12,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 18,75</t>
+          <t>-6,26; 16,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,1; -0,25</t>
+          <t>-22,1; -0,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,1; 7,2</t>
+          <t>-18,23; 8,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,87; 33,67</t>
+          <t>-23,4; 33,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 52,08</t>
+          <t>-12,48; 44,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-39,23; -0,49</t>
+          <t>-41,55; -0,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-39,59; 22,35</t>
+          <t>-39,52; 28,73</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,91; -15,23</t>
+          <t>-42,13; -16,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-24,01; 11,09</t>
+          <t>-24,27; 9,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-30,02; 1,12</t>
+          <t>-30,3; 1,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-32,12; -5,38</t>
+          <t>-31,25; -3,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-67,24; -31,93</t>
+          <t>-68,28; -31,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-41,78; 25,05</t>
+          <t>-41,67; 21,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-55,28; 2,08</t>
+          <t>-55,79; 3,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-74,98; -17,8</t>
+          <t>-73,7; -12,02</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,91; -4,78</t>
+          <t>-14,69; -5,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,34; -3,31</t>
+          <t>-13,41; -3,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,82; -3,74</t>
+          <t>-14,25; -4,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,26; -4,93</t>
+          <t>-16,5; -4,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-29,27; -11,53</t>
+          <t>-30,8; -12,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,09; -6,92</t>
+          <t>-25,51; -7,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-30,62; -9,18</t>
+          <t>-30,57; -10,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-39,15; -13,38</t>
+          <t>-40,93; -13,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_R2-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,8</t>
+          <t>-5,69</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-17,41%</t>
+          <t>-19,83%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 10,11</t>
+          <t>-12,0; 11,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 8,64</t>
+          <t>-19,99; 9,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 0,46</t>
+          <t>-27,06; 0,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 5,28</t>
+          <t>-16,47; 4,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,08; 33,77</t>
+          <t>-28,44; 38,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,0; 20,27</t>
+          <t>-34,56; 23,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-53,64; 0,03</t>
+          <t>-53,97; 1,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-48,26; 23,94</t>
+          <t>-47,51; 21,89</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-11,29</t>
+          <t>-11,99</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-27,37%</t>
+          <t>-28,75%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,9; 7,96</t>
+          <t>-17,5; 6,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,91; -8,13</t>
+          <t>-34,79; -9,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,71; -2,86</t>
+          <t>-26,39; -3,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,97; 0,5</t>
+          <t>-25,28; 0,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,43; 25,84</t>
+          <t>-39,32; 20,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-56,89; -17,43</t>
+          <t>-57,98; -19,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-57,73; -5,87</t>
+          <t>-60,11; -9,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,76; 2,37</t>
+          <t>-53,44; 0,08</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-9,49</t>
+          <t>-10,33</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-21,56%</t>
+          <t>-23,27%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-30,41; -4,47</t>
+          <t>-30,46; -4,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-27,69; 0,27</t>
+          <t>-27,74; 1,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-30,0; -1,82</t>
+          <t>-30,36; -0,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-27,5; 7,96</t>
+          <t>-27,31; 6,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-56,45; -10,04</t>
+          <t>-55,22; -10,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,98; 2,32</t>
+          <t>-50,44; 4,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-57,11; -4,04</t>
+          <t>-58,75; -1,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-52,69; 23,1</t>
+          <t>-53,68; 17,62</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-14,06</t>
+          <t>-10,83</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-31,54%</t>
+          <t>-24,46%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,16; -1,92</t>
+          <t>-19,47; -2,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,18; -2,03</t>
+          <t>-19,85; -1,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 9,34</t>
+          <t>-8,65; 9,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,29; -1,99</t>
+          <t>-20,62; -0,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,67; -4,61</t>
+          <t>-36,47; -4,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,56; -4,07</t>
+          <t>-34,42; -2,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,48; 25,71</t>
+          <t>-19,52; 27,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,74; -5,3</t>
+          <t>-41,92; -2,15</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-5,36</t>
+          <t>-7,14</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-13,69%</t>
+          <t>-18,4%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 12,64</t>
+          <t>-10,5; 11,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 16,3</t>
+          <t>-5,85; 17,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,1; -0,23</t>
+          <t>-21,51; -0,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 8,37</t>
+          <t>-18,84; 4,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,4; 33,86</t>
+          <t>-22,46; 29,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 44,54</t>
+          <t>-11,67; 48,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-41,55; -0,54</t>
+          <t>-39,93; -0,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-39,52; 28,73</t>
+          <t>-42,03; 15,38</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-18,87</t>
+          <t>-21,64</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-53,28%</t>
+          <t>-58,02%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-42,13; -16,22</t>
+          <t>-41,95; -13,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 9,63</t>
+          <t>-23,26; 9,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-30,3; 1,46</t>
+          <t>-30,32; 0,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,25; -3,03</t>
+          <t>-35,04; -8,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-68,28; -31,88</t>
+          <t>-66,72; -29,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-41,67; 21,97</t>
+          <t>-40,25; 24,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-55,79; 3,54</t>
+          <t>-54,84; 1,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-73,7; -12,02</t>
+          <t>-77,63; -23,74</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-10,47</t>
+          <t>-10,61</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-26,84%</t>
+          <t>-26,94%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,69; -5,61</t>
+          <t>-14,67; -5,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,41; -3,42</t>
+          <t>-13,51; -3,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,25; -4,37</t>
+          <t>-14,22; -4,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,5; -4,63</t>
+          <t>-15,21; -4,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-30,8; -12,99</t>
+          <t>-31,12; -11,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,51; -7,07</t>
+          <t>-25,27; -7,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-30,57; -10,5</t>
+          <t>-30,96; -11,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-40,93; -13,25</t>
+          <t>-36,63; -14,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_R2-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -522,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as</t>
+          <t>Población con sobrepeso u obesidad declarado por madres/padres</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-1,15</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-4,67</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-14,17</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-5,69</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-3,17%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-9,53%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-31,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-19,83%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-1.15141919099998</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-4.673054470658839</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-14.17147926916342</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-5.686898558674458</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.03173519854801711</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.09528894048228567</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.3101873949250539</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.1982732746822181</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-12,0; 11,09</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-19,99; 9,56</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-27,06; 0,87</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-16,47; 4,6</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-28,44; 38,67</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-34,56; 23,92</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-53,97; 1,93</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-47,51; 21,89</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-11.99520897240163</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-19.98907006740071</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-27.05916040469303</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-16.47187499947875</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2843985307912951</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.3456027583570049</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.539745787198585</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.4750990906140373</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11.09147080703256</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>9.563570182557173</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.8716541076054659</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4.597293947147723</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.3867489398976837</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.239171483389703</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.01925175126085334</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.218921136765703</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-5,33</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-22,13</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-14,87</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-11,99</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-13,98%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-39,66%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-39,09%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-28,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-17,5; 6,56</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-34,79; -9,55</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-26,39; -3,29</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-25,28; 0,1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-39,32; 20,6</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-57,98; -19,66</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-60,11; -9,28</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-53,44; 0,08</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-5.332360477378856</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-22.12505966803124</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-14.86520245825681</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-11.98714543237923</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1398156142137846</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.3966105327450055</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.3908962626120405</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.2874585404022705</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-18,17</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-14,56</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-16,35</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-10,33</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-35,95%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-29,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-35,27%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-23,27%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-17.4978190231617</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-34.79268283278159</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-26.39052602032764</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-25.27519092987831</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.393165247631105</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5798095887986641</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.6010622911084497</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.5343715901598903</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-30,46; -4,48</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-27,74; 1,79</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-30,36; -0,98</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-27,31; 6,58</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-55,22; -10,04</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-50,44; 4,84</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-58,75; -1,72</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-53,68; 17,62</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>6.56423923943933</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>-9.545157537111798</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>-3.288008878418435</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.09875225785891165</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.2059936135373633</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.1966139968418148</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>-0.09276866276540924</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.0007824384295357491</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-10,39</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-10,87</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-10,83</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-21,43%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-20,02%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-24,46%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-18.16964254263028</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-14.55839799521308</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-16.34882386464397</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-10.32768472362606</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.3594616137500459</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.2957737348401764</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.3526654560975866</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.2326833399430271</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-19,47; -2,08</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-19,85; -1,51</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-8,65; 9,84</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-20,62; -0,9</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-36,47; -4,55</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-34,42; -2,61</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-19,52; 27,13</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-41,92; -2,15</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-30.45573237929433</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-27.74334214718519</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-30.35715945725041</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-27.30538839516291</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.5522326405241996</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.5043933182787448</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.5875444408059574</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.5367914832688759</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-4.477992880550672</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.786557083928954</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-0.9824447951728503</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>6.584437621010094</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>-0.1004414604749442</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.04838507042959353</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>-0.01721504936030763</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.176210015545863</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,14</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>5,81</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-10,97</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-7,14</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>13,53%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-22,95%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-18,4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-10,5; 11,14</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-5,85; 17,38</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-21,51; -0,45</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-18,84; 4,77</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-22,46; 29,39</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-11,67; 48,31</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-39,93; -0,99</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-42,03; 15,38</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-10.38678451085537</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-10.86556149101726</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.179639391376929</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-10.83174136639304</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.2142584734816216</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2001841704675339</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.004414916633268312</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.2445831433840542</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-28,86</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-6,84</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-14,56</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-21,64</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-51,79%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-13,4%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-29,92%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-58,02%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-19.47392537597689</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-19.85264679305649</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-8.653500547461698</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-20.62458850550628</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3647474363601482</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3441717091412531</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1951639406720811</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.4191675563241407</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-41,95; -13,64</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-23,26; 9,98</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-30,32; 0,5</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-35,04; -8,1</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-66,72; -29,38</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-40,25; 24,91</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-54,84; 1,34</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-77,63; -23,74</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-2.084704960646561</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-1.513212129929783</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>9.835097277977454</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-0.8980234776748358</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-0.04549063085454135</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.02609613468831562</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.2713300445747497</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>-0.02152921696634031</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-9,72</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-8,48</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-9,26</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-10,61</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-21,4%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-16,69%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-21,16%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-26,94%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>0.1428169807613622</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>5.811771179708902</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-10.97486562774185</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-7.144318762258917</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.003341620449614761</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.1352831437205176</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.2294535412132594</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.1839669807198216</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-14,67; -5,06</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-13,51; -3,7</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-14,22; -4,56</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-15,21; -4,99</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-31,12; -11,71</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-25,27; -7,57</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-30,96; -11,07</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-36,63; -14,12</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-10.49917907481879</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-5.853006297813361</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-21.50510850161438</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-18.8387365487201</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.2246038246906024</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.116740347832455</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.3992985357960167</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.4203306306634175</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>11.14219782487104</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>17.38029889432239</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-0.4543423625191003</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>4.772625882189371</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.2939245655764809</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.4831439868207321</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>-0.00992796377136972</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.1537670271048471</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-28.85976808742364</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-6.83502144447905</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-14.5572803350687</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-21.63591928307841</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.5178954549605488</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.1339955194848581</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>-0.299150449637945</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.580214835342415</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-41.9461989808712</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-23.25774759630982</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-30.32008946488545</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-35.04499950228686</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.6671651732939778</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.4024831164776843</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.5483658041770912</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.7762550923794802</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>-13.64401584144506</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>9.983445470298189</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0.5027467356660319</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-8.102932131476196</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>-0.293782539939499</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.2491131190211461</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.01342535031272884</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>-0.2373998608276565</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-9.716689912941023</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-8.482701778757363</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-9.261741714708515</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-10.61250651509099</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.2140047421626178</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.1668745109491243</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.2115608051718143</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.2694047805505311</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-14.67477254947392</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-13.51329443411345</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-14.222836199951</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-15.20750600668624</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.3111777561723855</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.2526861343038774</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.3096062975108966</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.3662529234213976</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>-5.060681772626995</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-3.701094437964261</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-4.560174630046717</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-4.990930935195892</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>-0.1171252199792907</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>-0.07565828217545814</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>-0.1107335929787195</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>-0.1411708446582796</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1317,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
